--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitioner-authorization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="177">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitioner-authorization</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,11 +387,13 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Liste des types d'autorisation</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J75-TypeAutorisation-RASS/FHIR/JDV-J75-TypeAutorisation-RASS</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -401,21 +403,6 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:type.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Liste des types d'autorisation</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J75-TypeAutorisation-RASS/FHIR/JDV-J75-TypeAutorisation-RASS</t>
-  </si>
-  <si>
     <t>Extension.extension:period</t>
   </si>
   <si>
@@ -441,25 +428,19 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod</t>
-  </si>
-  <si>
-    <t>valuePeriod</t>
-  </si>
-  <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.id</t>
+    <t>Extension.extension:period.value[x].id</t>
   </si>
   <si>
     <t>Extension.extension.value[x].id</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.extension</t>
+    <t>Extension.extension:period.value[x].extension</t>
   </si>
   <si>
     <t>Extension.extension.value[x].extension</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.start</t>
+    <t>Extension.extension:period.value[x].start</t>
   </si>
   <si>
     <t>Extension.extension.value[x].start</t>
@@ -491,7 +472,7 @@
     <t>./low</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.end</t>
+    <t>Extension.extension:period.value[x].end</t>
   </si>
   <si>
     <t>Extension.extension.value[x].end</t>
@@ -539,9 +520,6 @@
     <t>Extension.extension:field.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:field.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
     <t>Liste des disciplines</t>
   </si>
   <si>
@@ -570,9 +548,6 @@
   </si>
   <si>
     <t>Extension.extension:profession.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:profession.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>Liste des professions</t>
@@ -884,12 +859,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK34"/>
+  <dimension ref="A1:AK30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="59.66015625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.71484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.25390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1828,29 +1803,31 @@
         <v>74</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1862,7 +1839,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>99</v>
@@ -1870,13 +1847,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
@@ -1898,13 +1875,13 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1931,13 +1908,13 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -1955,34 +1932,32 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2003,13 +1978,13 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2060,30 +2035,30 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2094,7 +2069,7 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2106,13 +2081,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2151,42 +2126,42 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2194,10 +2169,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2209,22 +2184,24 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2254,42 +2231,42 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2297,7 +2274,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>82</v>
@@ -2312,24 +2289,22 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>74</v>
@@ -2371,19 +2346,19 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>99</v>
@@ -2391,10 +2366,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2417,13 +2392,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2462,17 +2437,19 @@
         <v>74</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2481,34 +2458,32 @@
         <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2520,15 +2495,17 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>137</v>
+        <v>90</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>74</v>
@@ -2565,31 +2542,31 @@
         <v>74</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>99</v>
@@ -2597,10 +2574,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2620,18 +2597,20 @@
         <v>74</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>74</v>
@@ -2680,7 +2659,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>86</v>
+        <v>145</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2689,32 +2668,32 @@
         <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>87</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2723,25 +2702,27 @@
         <v>74</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q18" s="2"/>
+      <c r="Q18" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="R18" t="s" s="2">
         <v>74</v>
       </c>
@@ -2773,44 +2754,46 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>99</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
@@ -2828,19 +2811,19 @@
         <v>74</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>149</v>
+        <v>103</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2890,30 +2873,30 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>151</v>
+        <v>97</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>153</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2933,27 +2916,23 @@
         <v>74</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>146</v>
+        <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q20" t="s" s="2">
-        <v>159</v>
-      </c>
+      <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
         <v>74</v>
       </c>
@@ -2997,7 +2976,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -3006,25 +2985,23 @@
         <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>161</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
@@ -3033,7 +3010,7 @@
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -3048,14 +3025,12 @@
         <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N21" t="s" s="2">
-        <v>165</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
@@ -3092,16 +3067,16 @@
         <v>74</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>97</v>
@@ -3124,10 +3099,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3135,7 +3110,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>82</v>
@@ -3150,22 +3125,24 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>74</v>
@@ -3207,10 +3184,10 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>82</v>
@@ -3222,15 +3199,15 @@
         <v>74</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3241,7 +3218,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3253,13 +3230,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3286,62 +3263,64 @@
         <v>74</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>82</v>
@@ -3356,16 +3335,16 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3373,7 +3352,7 @@
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>74</v>
@@ -3415,30 +3394,30 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3461,13 +3440,13 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3506,17 +3485,19 @@
         <v>74</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC25" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3525,25 +3506,23 @@
         <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
@@ -3552,7 +3531,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3564,13 +3543,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3597,64 +3576,62 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>171</v>
+        <v>74</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>82</v>
@@ -3669,16 +3646,16 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3686,7 +3663,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>74</v>
@@ -3728,30 +3705,30 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3774,13 +3751,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3807,13 +3784,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3831,7 +3808,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3840,21 +3817,21 @@
         <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3862,10 +3839,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
@@ -3877,22 +3854,24 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="S29" t="s" s="2">
         <v>74</v>
@@ -3922,42 +3901,42 @@
         <v>74</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3965,10 +3944,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>74</v>
@@ -3980,24 +3959,22 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>111</v>
+        <v>176</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>74</v>
@@ -4039,435 +4016,21 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E31" s="2"/>
-      <c r="F31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K31" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
-      <c r="P31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q31" s="2"/>
-      <c r="R31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC31" s="2"/>
-      <c r="AD31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="D32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X32" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="Y32" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K33" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O33" s="2"/>
-      <c r="P33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K34" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
-      <c r="P34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK34" t="s" s="2">
         <v>99</v>
       </c>
     </row>
